--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>243.5577</v>
+        <v>10951.47</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>414.2016</v>
+        <v>18624.4</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>198.94</v>
+        <v>8945.25</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>651</v>
+        <v>29271.95</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>235.4295</v>
+        <v>10585.99</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>697.5</v>
+        <v>31362.8</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1033.05</v>
+        <v>46450.67</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>920</v>
+        <v>41367.42</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1033.05</v>
+        <v>46450.67</v>
       </c>
     </row>
     <row r="11">
@@ -1118,11 +1118,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>161.51989</v>
+        <v>7262.67</v>
       </c>
     </row>
     <row r="12">
@@ -1179,11 +1179,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>11067.5</v>
+        <v>497645.55</v>
       </c>
     </row>
     <row r="13">
@@ -1240,11 +1240,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>864.8</v>
+        <v>38885.37</v>
       </c>
     </row>
     <row r="14">
@@ -1301,11 +1301,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>723.24</v>
+        <v>32520.19</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>308.7</v>
+        <v>13880.57</v>
       </c>
     </row>
     <row r="16">
@@ -1423,11 +1423,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>814.3357</v>
+        <v>36616.27</v>
       </c>
     </row>
     <row r="17">
@@ -1484,11 +1484,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>517.9356</v>
+        <v>23288.76</v>
       </c>
     </row>
     <row r="18">
@@ -1545,11 +1545,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>566.2</v>
+        <v>25458.95</v>
       </c>
     </row>
     <row r="19">
@@ -1606,11 +1606,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1190.35</v>
+        <v>53523.59</v>
       </c>
     </row>
     <row r="20">
@@ -1667,11 +1667,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>813.192</v>
+        <v>36564.84</v>
       </c>
     </row>
     <row r="21">
@@ -1728,11 +1728,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>163.1375</v>
+        <v>7335.41</v>
       </c>
     </row>
     <row r="22">
@@ -1789,11 +1789,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>282.7618</v>
+        <v>12714.27</v>
       </c>
     </row>
     <row r="23">
@@ -1850,11 +1850,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1368.96</v>
+        <v>61554.72</v>
       </c>
     </row>
     <row r="24">
@@ -1911,11 +1911,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>294.5</v>
+        <v>13242.07</v>
       </c>
     </row>
     <row r="25">
@@ -1972,11 +1972,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>163.2529</v>
+        <v>7340.6</v>
       </c>
     </row>
     <row r="26">
@@ -2033,11 +2033,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2355.2</v>
+        <v>105900.59</v>
       </c>
     </row>
     <row r="27">
@@ -2094,11 +2094,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>758.4</v>
+        <v>34101.14</v>
       </c>
     </row>
     <row r="28">
@@ -2155,11 +2155,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>195.6364</v>
+        <v>8796.709999999999</v>
       </c>
     </row>
     <row r="29">
@@ -2216,11 +2216,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>287.14</v>
+        <v>12911.13</v>
       </c>
     </row>
     <row r="30">
@@ -2277,11 +2277,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>13179.03</v>
+        <v>592589.62</v>
       </c>
     </row>
     <row r="31">
@@ -2338,11 +2338,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>189.72</v>
+        <v>8530.68</v>
       </c>
     </row>
     <row r="32">
@@ -2399,11 +2399,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1450.84</v>
+        <v>65236.42</v>
       </c>
     </row>
     <row r="33">
@@ -2464,11 +2464,11 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>324000000</v>
+        <v>360947.33</v>
       </c>
     </row>
     <row r="34">
@@ -2525,11 +2525,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>163.1497</v>
+        <v>7335.96</v>
       </c>
     </row>
     <row r="35">
@@ -2586,11 +2586,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>892.4</v>
+        <v>40126.4</v>
       </c>
     </row>
     <row r="36">
@@ -2647,11 +2647,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>952.1816</v>
+        <v>42814.45</v>
       </c>
     </row>
     <row r="37">
@@ -2708,11 +2708,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>504</v>
+        <v>22662.15</v>
       </c>
     </row>
     <row r="38">
@@ -2773,11 +2773,11 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>36500.004</v>
+        <v>1641207.55</v>
       </c>
     </row>
     <row r="39">
@@ -2834,11 +2834,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>729.6982</v>
+        <v>32810.58</v>
       </c>
     </row>
     <row r="40">
@@ -2895,11 +2895,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>6969.6</v>
+        <v>313385.18</v>
       </c>
     </row>
     <row r="41">
@@ -2956,11 +2956,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>413.7984</v>
+        <v>18606.27</v>
       </c>
     </row>
     <row r="42">
@@ -3017,11 +3017,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1273.28</v>
+        <v>57252.51</v>
       </c>
     </row>
     <row r="43">
@@ -3078,11 +3078,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1410</v>
+        <v>63400.07</v>
       </c>
     </row>
     <row r="44">
@@ -3139,11 +3139,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1577.6068</v>
+        <v>70936.44</v>
       </c>
     </row>
     <row r="45">
@@ -3200,11 +3200,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>308.9832</v>
+        <v>13893.3</v>
       </c>
     </row>
     <row r="46">
@@ -3261,11 +3261,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>302.25</v>
+        <v>13590.55</v>
       </c>
     </row>
     <row r="47">
@@ -3322,11 +3322,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>245.3038</v>
+        <v>11029.98</v>
       </c>
     </row>
     <row r="48">
@@ -3383,11 +3383,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>255.75</v>
+        <v>11499.69</v>
       </c>
     </row>
     <row r="49">
@@ -3444,11 +3444,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1259.48</v>
+        <v>56632</v>
       </c>
     </row>
     <row r="50">
@@ -3505,11 +3505,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1104</v>
+        <v>49640.9</v>
       </c>
     </row>
     <row r="51">
@@ -3566,11 +3566,11 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2418.598</v>
+        <v>108751.26</v>
       </c>
     </row>
     <row r="52">
@@ -3627,11 +3627,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>627.6768</v>
+        <v>28223.23</v>
       </c>
     </row>
   </sheetData>
